--- a/src/Tests/Templates/Company.xlsx
+++ b/src/Tests/Templates/Company.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
-  <workbookPr showInkAnnotation="0"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr showInkAnnotation="0" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkDirectum\Tasks\RUI-38\rx-util-importdata-net-core\src\Tests\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RX253\git_repository\rx-util-importdata-net-core\src\Tests\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1BDD16-ABFE-462B-AB9E-702402048FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="НашиОрганизации" sheetId="7" r:id="rId1"/>
@@ -27,13 +26,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Попова Елена  (Popova_EI)</author>
     <author>Зорина Елена (Zorina_EV)</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +46,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -191,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -219,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -233,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -252,12 +251,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Зорина Елена (Zorina_EV)</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -286,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -328,14 +327,14 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Зорина Елена (Zorina_EV)</author>
     <author>Токмурзин Павел  (Tokmurzin_PV)</author>
     <author>Попова Елена  (Popova_EI)</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -349,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -363,7 +362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -377,7 +376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="G1" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -393,7 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="H1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -407,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="I1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="K1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="L1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -449,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="P1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -464,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -479,7 +478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -749,9 +748,6 @@
     <t>Иванович</t>
   </si>
   <si>
-    <t>ivan@comp.ru</t>
-  </si>
-  <si>
     <t>Генеральный директор</t>
   </si>
   <si>
@@ -837,13 +833,16 @@
   </si>
   <si>
     <t>id006</t>
+  </si>
+  <si>
+    <t>ironman@avengers.us</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -881,6 +880,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="7">
@@ -972,10 +977,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1007,9 +1013,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1354,35 +1362,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="34.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="55.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="58.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1444,7 +1452,7 @@
         <v>23</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="V1" s="10" t="s">
         <v>36</v>
@@ -1456,7 +1464,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1494,15 +1502,15 @@
         <v>47</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
       <c r="X2" s="14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1540,16 +1548,16 @@
         <v>52</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1557,21 +1565,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.08984375" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" customWidth="1"/>
-    <col min="8" max="8" width="36.6328125" customWidth="1"/>
-    <col min="9" max="9" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="36.5703125" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1597,7 +1605,7 @@
         <v>2</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>36</v>
@@ -1609,7 +1617,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1620,16 +1628,16 @@
         <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
     </row>
-    <row r="3" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1643,13 +1651,13 @@
         <v>57</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1663,13 +1671,13 @@
         <v>41</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1680,16 +1688,16 @@
         <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1697,24 +1705,24 @@
         <v>39</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:L8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1722,35 +1730,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.08984375" customWidth="1"/>
-    <col min="2" max="2" width="33.08984375" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
-    <col min="9" max="9" width="19.453125" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="21.453125" customWidth="1"/>
-    <col min="12" max="12" width="21.08984375" customWidth="1"/>
-    <col min="13" max="13" width="34.453125" customWidth="1"/>
-    <col min="14" max="14" width="32.08984375" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="24.08984375" customWidth="1"/>
-    <col min="20" max="20" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.36328125" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" customWidth="1"/>
+    <col min="13" max="13" width="34.42578125" customWidth="1"/>
+    <col min="14" max="14" width="32.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="24.140625" customWidth="1"/>
+    <col min="20" max="20" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -1812,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="V1" s="10" t="s">
         <v>36</v>
@@ -1824,7 +1832,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1853,13 +1861,13 @@
         <v>69</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>70</v>
       </c>
@@ -1879,13 +1887,13 @@
         <v>75</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
     </row>
-    <row r="4" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1905,13 +1913,13 @@
         <v>78</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
     </row>
-    <row r="5" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1933,17 +1941,17 @@
       <c r="G5" t="s">
         <v>67</v>
       </c>
-      <c r="P5" t="s">
-        <v>83</v>
+      <c r="P5" s="15" t="s">
+        <v>112</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
     </row>
-    <row r="6" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1951,22 +1959,22 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
         <v>84</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>85</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>86</v>
-      </c>
-      <c r="F6" t="s">
-        <v>87</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I6" s="6">
         <v>330500938709</v>
@@ -1975,31 +1983,31 @@
         <v>16530018028</v>
       </c>
       <c r="K6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" t="s">
         <v>89</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>90</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>91</v>
       </c>
-      <c r="O6" t="s">
+      <c r="R6" t="s">
         <v>92</v>
-      </c>
-      <c r="R6" t="s">
-        <v>93</v>
       </c>
       <c r="S6" s="6">
         <v>4.0817810099910001E+19</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -2007,74 +2015,77 @@
         <v>55</v>
       </c>
       <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
         <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
     </row>
-    <row r="9" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
     </row>
-    <row r="10" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
     </row>
-    <row r="11" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
     </row>
-    <row r="12" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
     </row>
-    <row r="13" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
     </row>
-    <row r="14" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
     </row>
-    <row r="15" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:X16" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="B1:X16"/>
+  <hyperlinks>
+    <hyperlink ref="P5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/src/Tests/Templates/Company.xlsx
+++ b/src/Tests/Templates/Company.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr showInkAnnotation="0" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RX253\git_repository\rx-util-importdata-net-core\src\Tests\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkDirectum\Tasks\RUI-38\rx-util-importdata-net-core\src\Tests\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1BDD16-ABFE-462B-AB9E-702402048FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="НашиОрганизации" sheetId="7" r:id="rId1"/>
@@ -26,13 +27,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Попова Елена  (Popova_EI)</author>
     <author>Зорина Елена (Zorina_EV)</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -46,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="1" shapeId="0">
+    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -60,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -97,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -134,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -162,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -176,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -190,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -204,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -218,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -232,7 +233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -251,12 +252,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Зорина Елена (Zorina_EV)</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -270,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -285,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -327,14 +328,14 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Зорина Елена (Zorina_EV)</author>
     <author>Токмурзин Павел  (Tokmurzin_PV)</author>
     <author>Попова Елена  (Popova_EI)</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -348,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -362,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -376,7 +377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -392,7 +393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0">
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -406,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="2" shapeId="0">
+    <comment ref="I1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -420,7 +421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0">
+    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -434,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="2" shapeId="0">
+    <comment ref="L1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -448,7 +449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2" shapeId="0">
+    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -463,7 +464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -478,7 +479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -748,6 +749,9 @@
     <t>Иванович</t>
   </si>
   <si>
+    <t>ivan@comp.ru</t>
+  </si>
+  <si>
     <t>Генеральный директор</t>
   </si>
   <si>
@@ -833,16 +837,13 @@
   </si>
   <si>
     <t>id006</t>
-  </si>
-  <si>
-    <t>ironman@avengers.us</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -880,12 +881,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="7">
@@ -977,11 +972,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1013,11 +1007,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1362,35 +1354,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="55.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="58.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1452,7 +1444,7 @@
         <v>23</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V1" s="10" t="s">
         <v>36</v>
@@ -1464,7 +1456,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1502,15 +1494,15 @@
         <v>47</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
       <c r="X2" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1548,16 +1540,16 @@
         <v>52</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X3"/>
+  <autoFilter ref="A1:X3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1565,21 +1557,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.08984375" customWidth="1"/>
+    <col min="5" max="5" width="30.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
+    <col min="8" max="8" width="36.6328125" customWidth="1"/>
+    <col min="9" max="9" width="27.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1605,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>36</v>
@@ -1617,7 +1609,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1628,16 +1620,16 @@
         <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1651,13 +1643,13 @@
         <v>57</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1671,13 +1663,13 @@
         <v>41</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1688,16 +1680,16 @@
         <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1705,24 +1697,24 @@
         <v>39</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="14" x14ac:dyDescent="0.4">
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L8" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1730,35 +1722,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="42.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.08984375" customWidth="1"/>
+    <col min="2" max="2" width="33.08984375" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.36328125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" customWidth="1"/>
-    <col min="12" max="12" width="21.140625" customWidth="1"/>
-    <col min="13" max="13" width="34.42578125" customWidth="1"/>
-    <col min="14" max="14" width="32.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="24.140625" customWidth="1"/>
-    <col min="20" max="20" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="21.453125" customWidth="1"/>
+    <col min="12" max="12" width="21.08984375" customWidth="1"/>
+    <col min="13" max="13" width="34.453125" customWidth="1"/>
+    <col min="14" max="14" width="32.08984375" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="24.08984375" customWidth="1"/>
+    <col min="20" max="20" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -1820,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V1" s="10" t="s">
         <v>36</v>
@@ -1832,7 +1824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1861,13 +1853,13 @@
         <v>69</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>70</v>
       </c>
@@ -1887,13 +1879,13 @@
         <v>75</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1913,13 +1905,13 @@
         <v>78</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1941,17 +1933,17 @@
       <c r="G5" t="s">
         <v>67</v>
       </c>
-      <c r="P5" s="15" t="s">
-        <v>112</v>
+      <c r="P5" t="s">
+        <v>83</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1959,22 +1951,22 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6" s="6">
         <v>330500938709</v>
@@ -1983,31 +1975,31 @@
         <v>16530018028</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S6" s="6">
         <v>4.0817810099910001E+19</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -2015,77 +2007,74 @@
         <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="14" x14ac:dyDescent="0.4">
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:X16"/>
-  <hyperlinks>
-    <hyperlink ref="P5" r:id="rId1"/>
-  </hyperlinks>
+  <autoFilter ref="B1:X16" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/src/Tests/Templates/Company.xlsx
+++ b/src/Tests/Templates/Company.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
-  <workbookPr showInkAnnotation="0"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr showInkAnnotation="0" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkDirectum\Tasks\RUI-38\rx-util-importdata-net-core\src\Tests\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Utilites\rx-util-importdata-net-core\src\Tests\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1BDD16-ABFE-462B-AB9E-702402048FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="НашиОрганизации" sheetId="7" r:id="rId1"/>
@@ -27,13 +26,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Попова Елена  (Popova_EI)</author>
     <author>Зорина Елена (Zorina_EV)</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +46,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -191,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -219,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -233,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -252,12 +251,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Зорина Елена (Zorina_EV)</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -286,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -328,14 +327,14 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Зорина Елена (Zorina_EV)</author>
     <author>Токмурзин Павел  (Tokmurzin_PV)</author>
     <author>Попова Елена  (Popova_EI)</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -349,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -363,7 +362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -377,7 +376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="G1" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -393,7 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="H1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -407,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="I1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="K1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="L1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -449,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="P1" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -464,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -479,7 +478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -842,7 +841,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1009,7 +1008,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1354,35 +1353,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="34.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="55.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="58.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1456,7 +1455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1502,7 +1501,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1549,7 +1548,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1557,21 +1556,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.08984375" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" customWidth="1"/>
-    <col min="8" max="8" width="36.6328125" customWidth="1"/>
-    <col min="9" max="9" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="36.5703125" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1609,7 +1608,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1629,7 +1628,7 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
     </row>
-    <row r="3" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1649,7 +1648,7 @@
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1669,7 +1668,7 @@
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1689,7 +1688,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1703,18 +1702,18 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:12" ht="14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:L8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1722,35 +1721,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.08984375" customWidth="1"/>
-    <col min="2" max="2" width="33.08984375" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
-    <col min="9" max="9" width="19.453125" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="21.453125" customWidth="1"/>
-    <col min="12" max="12" width="21.08984375" customWidth="1"/>
-    <col min="13" max="13" width="34.453125" customWidth="1"/>
-    <col min="14" max="14" width="32.08984375" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="24.08984375" customWidth="1"/>
-    <col min="20" max="20" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.36328125" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" customWidth="1"/>
+    <col min="13" max="13" width="34.42578125" customWidth="1"/>
+    <col min="14" max="14" width="32.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="24.140625" customWidth="1"/>
+    <col min="20" max="20" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -1824,7 +1823,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1859,7 +1858,7 @@
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>70</v>
       </c>
@@ -1885,7 +1884,7 @@
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
     </row>
-    <row r="4" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1911,7 +1910,7 @@
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
     </row>
-    <row r="5" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1943,7 +1942,7 @@
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
     </row>
-    <row r="6" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1999,7 +1998,7 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -2031,48 +2030,48 @@
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
     </row>
-    <row r="9" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
     </row>
-    <row r="10" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
     </row>
-    <row r="11" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
     </row>
-    <row r="12" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
     </row>
-    <row r="13" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
     </row>
-    <row r="14" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
     </row>
-    <row r="15" spans="1:24" ht="14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:X16" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="B1:X16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
